--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,42 +442,298 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>-100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-100</v>
+        <v>160</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-100</v>
+        <v>220</v>
       </c>
       <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>340</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>400</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>460</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>520</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>580</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>640</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>700</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>760</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>820</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>880</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>940</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>940</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>880</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>820</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>760</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>700</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>640</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>580</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>520</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>460</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>400</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>340</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>280</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>220</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>160</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>100</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -442,10 +442,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="B2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>160</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>220</v>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>280</v>
       </c>
       <c r="B7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>340</v>
       </c>
       <c r="B8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>400</v>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>460</v>
       </c>
       <c r="B10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>520</v>
       </c>
       <c r="B11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>580</v>
       </c>
       <c r="B12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>640</v>
       </c>
       <c r="B13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>700</v>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>760</v>
       </c>
       <c r="B15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>820</v>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>880</v>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -573,23 +573,23 @@
         <v>940</v>
       </c>
       <c r="B18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="B20" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>940</v>
       </c>
       <c r="B21" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>880</v>
       </c>
       <c r="B22" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>820</v>
       </c>
       <c r="B23" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>760</v>
       </c>
       <c r="B24" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>700</v>
       </c>
       <c r="B25" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>640</v>
       </c>
       <c r="B26" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>580</v>
       </c>
       <c r="B27" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>520</v>
       </c>
       <c r="B28" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>460</v>
       </c>
       <c r="B29" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>400</v>
       </c>
       <c r="B30" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>340</v>
       </c>
       <c r="B31" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>280</v>
       </c>
       <c r="B32" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>220</v>
       </c>
       <c r="B33" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>160</v>
       </c>
       <c r="B34" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>100</v>
       </c>
       <c r="B35" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="36">
@@ -717,23 +717,23 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="B37" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="B38" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40</v>
+        <v>1500</v>
       </c>
       <c r="B3" t="n">
         <v>500</v>
@@ -458,281 +458,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="B4" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>160</v>
+        <v>-500</v>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>220</v>
+        <v>-500</v>
       </c>
       <c r="B6" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>280</v>
-      </c>
-      <c r="B7" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>340</v>
-      </c>
-      <c r="B8" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>400</v>
-      </c>
-      <c r="B9" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>460</v>
-      </c>
-      <c r="B10" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>520</v>
-      </c>
-      <c r="B11" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>580</v>
-      </c>
-      <c r="B12" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>640</v>
-      </c>
-      <c r="B13" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>700</v>
-      </c>
-      <c r="B14" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>760</v>
-      </c>
-      <c r="B15" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>820</v>
-      </c>
-      <c r="B16" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>880</v>
-      </c>
-      <c r="B17" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>940</v>
-      </c>
-      <c r="B18" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="B19" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="B20" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>940</v>
-      </c>
-      <c r="B21" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>880</v>
-      </c>
-      <c r="B22" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>820</v>
-      </c>
-      <c r="B23" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>760</v>
-      </c>
-      <c r="B24" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>700</v>
-      </c>
-      <c r="B25" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>640</v>
-      </c>
-      <c r="B26" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>580</v>
-      </c>
-      <c r="B27" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>520</v>
-      </c>
-      <c r="B28" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>460</v>
-      </c>
-      <c r="B29" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>400</v>
-      </c>
-      <c r="B30" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>340</v>
-      </c>
-      <c r="B31" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>280</v>
-      </c>
-      <c r="B32" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>220</v>
-      </c>
-      <c r="B33" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>160</v>
-      </c>
-      <c r="B34" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>100</v>
-      </c>
-      <c r="B35" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>40</v>
-      </c>
-      <c r="B36" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>-500</v>
-      </c>
-      <c r="B37" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>-500</v>
-      </c>
-      <c r="B38" t="n">
         <v>500</v>
       </c>
     </row>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -442,10 +442,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="B2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>160</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>220</v>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>280</v>
       </c>
       <c r="B7" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>340</v>
       </c>
       <c r="B8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>400</v>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>460</v>
       </c>
       <c r="B10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>520</v>
       </c>
       <c r="B11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>580</v>
       </c>
       <c r="B12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>640</v>
       </c>
       <c r="B13" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>700</v>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>760</v>
       </c>
       <c r="B15" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>820</v>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>880</v>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -573,23 +573,23 @@
         <v>940</v>
       </c>
       <c r="B18" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="B20" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>940</v>
       </c>
       <c r="B21" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>880</v>
       </c>
       <c r="B22" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>820</v>
       </c>
       <c r="B23" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>760</v>
       </c>
       <c r="B24" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>700</v>
       </c>
       <c r="B25" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>640</v>
       </c>
       <c r="B26" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>580</v>
       </c>
       <c r="B27" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>520</v>
       </c>
       <c r="B28" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>460</v>
       </c>
       <c r="B29" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>400</v>
       </c>
       <c r="B30" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>340</v>
       </c>
       <c r="B31" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>280</v>
       </c>
       <c r="B32" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>220</v>
       </c>
       <c r="B33" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>160</v>
       </c>
       <c r="B34" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>100</v>
       </c>
       <c r="B35" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="36">
@@ -717,23 +717,23 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="B37" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="B38" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -442,10 +442,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="B2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>160</v>
       </c>
       <c r="B5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>220</v>
       </c>
       <c r="B6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>280</v>
       </c>
       <c r="B7" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>340</v>
       </c>
       <c r="B8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>400</v>
       </c>
       <c r="B9" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>460</v>
       </c>
       <c r="B10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>520</v>
       </c>
       <c r="B11" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>580</v>
       </c>
       <c r="B12" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>640</v>
       </c>
       <c r="B13" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>700</v>
       </c>
       <c r="B14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>760</v>
       </c>
       <c r="B15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>820</v>
       </c>
       <c r="B16" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>880</v>
       </c>
       <c r="B17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -573,23 +573,23 @@
         <v>940</v>
       </c>
       <c r="B18" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="B19" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="B20" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>940</v>
       </c>
       <c r="B21" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>880</v>
       </c>
       <c r="B22" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>820</v>
       </c>
       <c r="B23" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>760</v>
       </c>
       <c r="B24" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>700</v>
       </c>
       <c r="B25" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>640</v>
       </c>
       <c r="B26" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>580</v>
       </c>
       <c r="B27" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>520</v>
       </c>
       <c r="B28" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>460</v>
       </c>
       <c r="B29" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>400</v>
       </c>
       <c r="B30" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>340</v>
       </c>
       <c r="B31" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>280</v>
       </c>
       <c r="B32" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>220</v>
       </c>
       <c r="B33" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>160</v>
       </c>
       <c r="B34" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>100</v>
       </c>
       <c r="B35" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="36">
@@ -717,23 +717,23 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="B37" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="B38" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -442,10 +442,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>160</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>220</v>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>280</v>
       </c>
       <c r="B7" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>340</v>
       </c>
       <c r="B8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>400</v>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>460</v>
       </c>
       <c r="B10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>520</v>
       </c>
       <c r="B11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>580</v>
       </c>
       <c r="B12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>640</v>
       </c>
       <c r="B13" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>700</v>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>760</v>
       </c>
       <c r="B15" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>820</v>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>880</v>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -573,23 +573,23 @@
         <v>940</v>
       </c>
       <c r="B18" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="B20" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>940</v>
       </c>
       <c r="B21" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>880</v>
       </c>
       <c r="B22" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>820</v>
       </c>
       <c r="B23" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>760</v>
       </c>
       <c r="B24" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>700</v>
       </c>
       <c r="B25" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>640</v>
       </c>
       <c r="B26" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>580</v>
       </c>
       <c r="B27" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>520</v>
       </c>
       <c r="B28" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>460</v>
       </c>
       <c r="B29" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>400</v>
       </c>
       <c r="B30" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>340</v>
       </c>
       <c r="B31" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>280</v>
       </c>
       <c r="B32" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>220</v>
       </c>
       <c r="B33" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>160</v>
       </c>
       <c r="B34" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>100</v>
       </c>
       <c r="B35" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="36">
@@ -717,23 +717,23 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="B37" t="n">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="B38" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -1,37 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>X_coordinate</t>
+  </si>
+  <si>
+    <t>Y_coordinate</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +60,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,323 +376,315 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>X_coordinate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Y_coordinate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
         <v>40</v>
       </c>
-      <c r="B3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
         <v>160</v>
       </c>
-      <c r="B5" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B5">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
         <v>220</v>
       </c>
-      <c r="B6" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
         <v>280</v>
       </c>
-      <c r="B7" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B7">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
         <v>340</v>
       </c>
-      <c r="B8" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
         <v>400</v>
       </c>
-      <c r="B9" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="B9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
         <v>460</v>
       </c>
-      <c r="B10" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="B10">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
         <v>520</v>
       </c>
-      <c r="B11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="B11">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
         <v>580</v>
       </c>
-      <c r="B12" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B12">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
         <v>640</v>
       </c>
-      <c r="B13" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="B13">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
         <v>700</v>
       </c>
-      <c r="B14" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="B14">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
         <v>760</v>
       </c>
-      <c r="B15" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="B15">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
         <v>820</v>
       </c>
-      <c r="B16" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="B16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
         <v>880</v>
       </c>
-      <c r="B17" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="B17">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
         <v>940</v>
       </c>
-      <c r="B18" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="B18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
         <v>1000</v>
       </c>
-      <c r="B19" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="B19">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
         <v>1000</v>
       </c>
-      <c r="B20" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="B20">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
         <v>940</v>
       </c>
-      <c r="B21" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="B21">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
         <v>880</v>
       </c>
-      <c r="B22" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="B22">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
         <v>820</v>
       </c>
-      <c r="B23" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="B23">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
         <v>760</v>
       </c>
-      <c r="B24" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="B24">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
         <v>700</v>
       </c>
-      <c r="B25" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="B25">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
         <v>640</v>
       </c>
-      <c r="B26" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="B26">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
         <v>580</v>
       </c>
-      <c r="B27" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="B27">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
         <v>520</v>
       </c>
-      <c r="B28" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="B28">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
         <v>460</v>
       </c>
-      <c r="B29" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="B29">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
         <v>400</v>
       </c>
-      <c r="B30" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="B30">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
         <v>340</v>
       </c>
-      <c r="B31" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="B31">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
         <v>280</v>
       </c>
-      <c r="B32" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="B32">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>220</v>
       </c>
-      <c r="B33" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="B33">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
         <v>160</v>
       </c>
-      <c r="B34" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="B34">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
         <v>100</v>
       </c>
-      <c r="B35" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="B35">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
         <v>40</v>
       </c>
-      <c r="B36" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="B36">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
         <v>0</v>
       </c>
-      <c r="B37" t="n">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="B37">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
         <v>0</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>600</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -393,7 +393,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>100</v>
       </c>
       <c r="B4">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>160</v>
       </c>
       <c r="B5">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>220</v>
       </c>
       <c r="B6">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>280</v>
       </c>
       <c r="B7">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>340</v>
       </c>
       <c r="B8">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>400</v>
       </c>
       <c r="B9">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>460</v>
       </c>
       <c r="B10">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>520</v>
       </c>
       <c r="B11">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>580</v>
       </c>
       <c r="B12">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -481,7 +481,7 @@
         <v>640</v>
       </c>
       <c r="B13">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -489,7 +489,7 @@
         <v>700</v>
       </c>
       <c r="B14">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -497,7 +497,7 @@
         <v>760</v>
       </c>
       <c r="B15">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -505,7 +505,7 @@
         <v>820</v>
       </c>
       <c r="B16">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -513,7 +513,7 @@
         <v>880</v>
       </c>
       <c r="B17">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -521,7 +521,7 @@
         <v>940</v>
       </c>
       <c r="B18">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -529,7 +529,7 @@
         <v>1000</v>
       </c>
       <c r="B19">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -537,7 +537,7 @@
         <v>1000</v>
       </c>
       <c r="B20">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -545,7 +545,7 @@
         <v>940</v>
       </c>
       <c r="B21">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -553,7 +553,7 @@
         <v>880</v>
       </c>
       <c r="B22">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -561,7 +561,7 @@
         <v>820</v>
       </c>
       <c r="B23">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -569,7 +569,7 @@
         <v>760</v>
       </c>
       <c r="B24">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -577,7 +577,7 @@
         <v>700</v>
       </c>
       <c r="B25">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -585,7 +585,7 @@
         <v>640</v>
       </c>
       <c r="B26">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -593,7 +593,7 @@
         <v>580</v>
       </c>
       <c r="B27">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -601,7 +601,7 @@
         <v>520</v>
       </c>
       <c r="B28">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -609,7 +609,7 @@
         <v>460</v>
       </c>
       <c r="B29">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -617,7 +617,7 @@
         <v>400</v>
       </c>
       <c r="B30">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -625,7 +625,7 @@
         <v>340</v>
       </c>
       <c r="B31">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -633,7 +633,7 @@
         <v>280</v>
       </c>
       <c r="B32">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -641,7 +641,7 @@
         <v>220</v>
       </c>
       <c r="B33">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -649,7 +649,7 @@
         <v>160</v>
       </c>
       <c r="B34">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -657,7 +657,7 @@
         <v>100</v>
       </c>
       <c r="B35">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -665,7 +665,7 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="B37">
-        <v>-600</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="B38">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/LGT Zone Boundary.xlsx
+++ b/Data/output/LGT Zone Boundary.xlsx
@@ -393,7 +393,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>100</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>160</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>220</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>280</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>340</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>400</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>460</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>520</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>580</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -481,7 +481,7 @@
         <v>640</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -489,7 +489,7 @@
         <v>700</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -497,7 +497,7 @@
         <v>760</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -505,7 +505,7 @@
         <v>820</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -513,7 +513,7 @@
         <v>880</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -521,7 +521,7 @@
         <v>940</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -529,7 +529,7 @@
         <v>1000</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -537,7 +537,7 @@
         <v>1000</v>
       </c>
       <c r="B20">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -545,7 +545,7 @@
         <v>940</v>
       </c>
       <c r="B21">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -553,7 +553,7 @@
         <v>880</v>
       </c>
       <c r="B22">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -561,7 +561,7 @@
         <v>820</v>
       </c>
       <c r="B23">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -569,7 +569,7 @@
         <v>760</v>
       </c>
       <c r="B24">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -577,7 +577,7 @@
         <v>700</v>
       </c>
       <c r="B25">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -585,7 +585,7 @@
         <v>640</v>
       </c>
       <c r="B26">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -593,7 +593,7 @@
         <v>580</v>
       </c>
       <c r="B27">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -601,7 +601,7 @@
         <v>520</v>
       </c>
       <c r="B28">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -609,7 +609,7 @@
         <v>460</v>
       </c>
       <c r="B29">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -617,7 +617,7 @@
         <v>400</v>
       </c>
       <c r="B30">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -625,7 +625,7 @@
         <v>340</v>
       </c>
       <c r="B31">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -633,7 +633,7 @@
         <v>280</v>
       </c>
       <c r="B32">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -641,7 +641,7 @@
         <v>220</v>
       </c>
       <c r="B33">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -649,7 +649,7 @@
         <v>160</v>
       </c>
       <c r="B34">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -657,7 +657,7 @@
         <v>100</v>
       </c>
       <c r="B35">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -665,7 +665,7 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="B37">
-        <v>-100</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
